--- a/results/3er_publaw.xlsx
+++ b/results/3er_publaw.xlsx
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D2" t="n">
-        <v>25.12562814070352</v>
+        <v>24.18604651162791</v>
       </c>
     </row>
     <row r="3">
@@ -461,13 +461,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>20.23809523809524</v>
+        <v>18.44660194174757</v>
       </c>
     </row>
     <row r="4">
